--- a/Lab Files/EventPlanning.xlsx
+++ b/Lab Files/EventPlanning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\breta\Dropbox\Courses\PowerApps-PowerUsers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://qalearning-my.sharepoint.com/personal/bappleby_qa_com/Documents/Courses/QA/QAPAESS/WIP/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800D935A-47BC-4A57-BD4D-5DFA33526DB5}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{800D935A-47BC-4A57-BD4D-5DFA33526DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DACC479-E643-4D14-91C0-AACE5C433C6E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{57C3D246-1470-49FE-9465-93ACB35249E6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{57C3D246-1470-49FE-9465-93ACB35249E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendees" sheetId="1" r:id="rId1"/>
@@ -34,9 +34,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="13">
   <si>
-    <t>Meal Choice</t>
-  </si>
-  <si>
     <t>Cost</t>
   </si>
   <si>
@@ -58,9 +55,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Special Instructions</t>
-  </si>
-  <si>
     <t>Alexandra Armatage</t>
   </si>
   <si>
@@ -71,6 +65,12 @@
   </si>
   <si>
     <t>No nuts</t>
+  </si>
+  <si>
+    <t>MealChoice</t>
+  </si>
+  <si>
+    <t>SpecialInstructions</t>
   </si>
 </sst>
 </file>
@@ -125,13 +125,17 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{4F534AA6-E550-4357-BB0B-5787EC2B60CC}" name="Attendees" displayName="Attendees" ref="A1:D3" totalsRowShown="0">
   <autoFilter ref="A1:D3" xr:uid="{D24E1168-AD9A-4051-B26C-E088FC0FCABC}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{78FE5CDE-E47B-4977-815D-BB08DDAC75C2}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{F156FB25-A0A6-40AB-8011-0B8BA58083CA}" name="Meal Choice"/>
-    <tableColumn id="3" xr3:uid="{E129A4CA-15EA-4E2E-8269-372A7D5E8E0F}" name="Special Instructions"/>
+    <tableColumn id="2" xr3:uid="{F156FB25-A0A6-40AB-8011-0B8BA58083CA}" name="MealChoice"/>
+    <tableColumn id="3" xr3:uid="{E129A4CA-15EA-4E2E-8269-372A7D5E8E0F}" name="SpecialInstructions"/>
     <tableColumn id="4" xr3:uid="{5CEBD1FB-9CAC-4670-BFBC-034E6E4AC72E}" name="Cost"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -142,7 +146,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{58EDCBF9-BE7A-4DC7-82E6-6DA0574EA6E7}" name="MealOptions" displayName="MealOptions" ref="A1:B6" totalsRowShown="0">
   <autoFilter ref="A1:B6" xr:uid="{D7102D0D-644A-4F4A-9F64-EF1B9DBC5C1C}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A9AD1F11-21F4-4996-BDF8-35ADDCED2057}" name="Meal Choice"/>
+    <tableColumn id="1" xr3:uid="{A9AD1F11-21F4-4996-BDF8-35ADDCED2057}" name="MealChoice"/>
     <tableColumn id="2" xr3:uid="{82638F56-E323-4252-9E59-0CD3D3269F12}" name="Cost"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -150,9 +154,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -190,7 +194,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -296,7 +300,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -438,7 +442,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -447,50 +451,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8242C1FE-75BE-455A-B15E-B775C28705DA}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.21875" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" customWidth="1"/>
+    <col min="1" max="1" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
         <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
       </c>
       <c r="D2">
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>5.26</v>
@@ -507,54 +511,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC424A06-C929-48BD-95E2-A1026E760762}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>2</v>
       </c>
       <c r="B2">
         <v>5.26</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>6.45</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>4.12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6">
         <v>4.87</v>
@@ -569,6 +573,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SequenceNumber xmlns="4F14B4B3-92AA-4256-88B1-2650A05DEF97">7</SequenceNumber>
+    <BookTypeField0 xmlns="4F14B4B3-92AA-4256-88B1-2650A05DEF97">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">IK</TermName>
+          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">5abe6401-e87a-4499-80b4-3d21a1a6ebd7</TermId>
+        </TermInfo>
+      </Terms>
+    </BookTypeField0>
+    <IsBuildFile xmlns="4F14B4B3-92AA-4256-88B1-2650A05DEF97" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Courseware" ma:contentTypeID="0x010100F0967B7CEE8D417F966757887D9466FB00BD063C06C41CC84E84FE9FB9422AD33A" ma:contentTypeVersion="0" ma:contentTypeDescription="Base content type which represents courseware documents" ma:contentTypeScope="" ma:versionID="5927dbd2e184ac29659e4913170ef8a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4F14B4B3-92AA-4256-88B1-2650A05DEF97" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ff06b15aeb157706c34b7f8842e17e8" ns2:_="">
     <xsd:import namespace="4F14B4B3-92AA-4256-88B1-2650A05DEF97"/>
@@ -708,7 +729,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -717,31 +738,44 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SequenceNumber xmlns="4F14B4B3-92AA-4256-88B1-2650A05DEF97">7</SequenceNumber>
-    <BookTypeField0 xmlns="4F14B4B3-92AA-4256-88B1-2650A05DEF97">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-        <TermInfo xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-          <TermName xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">IK</TermName>
-          <TermId xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">5abe6401-e87a-4499-80b4-3d21a1a6ebd7</TermId>
-        </TermInfo>
-      </Terms>
-    </BookTypeField0>
-    <IsBuildFile xmlns="4F14B4B3-92AA-4256-88B1-2650A05DEF97" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{067D3C44-0C0B-490B-B051-1D968AE3E3C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{553C7529-BA84-408B-9CDC-07F1C6C5A037}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4F14B4B3-92AA-4256-88B1-2650A05DEF97"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1656BFF8-4EB4-44CD-A3BB-6387B98F0ED3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{067D3C44-0C0B-490B-B051-1D968AE3E3C5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4F14B4B3-92AA-4256-88B1-2650A05DEF97"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{553C7529-BA84-408B-9CDC-07F1C6C5A037}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1656BFF8-4EB4-44CD-A3BB-6387B98F0ED3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{9c220797-c337-49f8-b086-a9a24979f728}" enabled="0" method="" siteId="{9c220797-c337-49f8-b086-a9a24979f728}" removed="1"/>
+</clbl:labelList>
 </file>